--- a/resultados/analisis_tabla_entropia.xlsx
+++ b/resultados/analisis_tabla_entropia.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos_D\etapa-analisis_pcsmote\resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FamiliaNatelloMedina\Desktop\codigo\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A78C4F9-D753-4937-A36E-C9B2EDCC4D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{27EB1403-4DE2-4C0A-BDBC-323C495BD8E9}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -59,20 +58,20 @@
     <t>k (cant vecinos)</t>
   </si>
   <si>
-    <t>-pmin*(LOG2(pmin))</t>
-  </si>
-  <si>
-    <t>-pmaj*(LOG2(pmaj))</t>
-  </si>
-  <si>
     <t>H(s) entropia total</t>
+  </si>
+  <si>
+    <t>pmaj*(LOG2(pmaj))</t>
+  </si>
+  <si>
+    <t>pmin*(LOG2(pmin))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,16 +115,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,66 +470,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCEB3183-712B-4BAA-80F9-46E770B2FFEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="15.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="B2">
         <f>LOG10(2)</f>
         <v>0.3010299956639812</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:7" s="8" customFormat="1" ht="28.5">
+      <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>0</v>
       </c>
@@ -526,19 +539,19 @@
         <v>7</v>
       </c>
       <c r="C6" s="2">
-        <f>A6/A$2</f>
+        <f t="shared" ref="C6:C13" si="0">A6/A$2</f>
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <f>B6/A$2</f>
+        <f t="shared" ref="D6:D13" si="1">B6/A$2</f>
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <f>C6*(IF(ISERROR(LOG10(C6)),0,LOG10(C6))/C$2)</f>
+        <f>C6*(IF(ISERROR(LOG10(C6)),0,LOG10(C6))/B$2)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <f>D6*(LOG10(D6)/C$2)</f>
+        <f>D6*(LOG10(D6)/B$2)</f>
         <v>0</v>
       </c>
       <c r="G6" s="2">
@@ -546,7 +559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -554,27 +567,27 @@
         <v>6</v>
       </c>
       <c r="C7" s="2">
-        <f>A7/A$2</f>
+        <f t="shared" si="0"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="D7" s="2">
-        <f>B7/A$2</f>
+        <f t="shared" si="1"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="E7" s="2">
-        <f>C7*(IF(ISERROR(LOG10(C7)),0,LOG10(C7))/C$2)</f>
+        <f>C7*(IF(ISERROR(LOG10(C7)),0,LOG10(C7))/B$2)</f>
         <v>-0.40105070315108626</v>
       </c>
       <c r="F7" s="2">
-        <f>D7*(LOG10(D7)/C$2)</f>
+        <f>D7*(LOG10(D7)/B$2)</f>
         <v>-0.19062207543124113</v>
       </c>
       <c r="G7" s="2">
-        <f t="shared" ref="G7:G13" si="0">-E7-F7</f>
+        <f t="shared" ref="G7:G13" si="2">-E7-F7</f>
         <v>0.59167277858232736</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -582,27 +595,27 @@
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <f>A8/A$2</f>
+        <f t="shared" si="0"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="D8" s="2">
-        <f>B8/A$2</f>
+        <f t="shared" si="1"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="E8" s="2">
-        <f>C8*(IF(ISERROR(LOG10(C8)),0,LOG10(C8))/C$2)</f>
+        <f>C8*(IF(ISERROR(LOG10(C8)),0,LOG10(C8))/B$2)</f>
         <v>-0.51638712058788683</v>
       </c>
       <c r="F8" s="2">
-        <f>D8*(LOG10(D8)/C$2)</f>
+        <f>D8*(LOG10(D8)/B$2)</f>
         <v>-0.34673344797874411</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.863120568566631</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -610,27 +623,27 @@
         <v>4</v>
       </c>
       <c r="C9" s="2">
-        <f>A9/A$2</f>
+        <f t="shared" si="0"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="D9" s="2">
-        <f>B9/A$2</f>
+        <f t="shared" si="1"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="E9" s="2">
-        <f>C9*(IF(ISERROR(LOG10(C9)),0,LOG10(C9))/C$2)</f>
+        <f>C9*(IF(ISERROR(LOG10(C9)),0,LOG10(C9))/B$2)</f>
         <v>-0.52388246628704915</v>
       </c>
       <c r="F9" s="2">
-        <f>D9*(LOG10(D9)/C$2)</f>
+        <f>D9*(LOG10(D9)/B$2)</f>
         <v>-0.46134566974720237</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.98522813603425152</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -638,27 +651,27 @@
         <v>3</v>
       </c>
       <c r="C10" s="2">
-        <f>A10/A$2</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="D10" s="2">
-        <f>B10/A$2</f>
+        <f t="shared" si="1"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="E10" s="2">
-        <f>C10*(IF(ISERROR(LOG10(C10)),0,LOG10(C10))/C$2)</f>
+        <f>C10*(IF(ISERROR(LOG10(C10)),0,LOG10(C10))/B$2)</f>
         <v>-0.46134566974720237</v>
       </c>
       <c r="F10" s="2">
-        <f>D10*(LOG10(D10)/C$2)</f>
+        <f>D10*(LOG10(D10)/B$2)</f>
         <v>-0.52388246628704915</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.98522813603425152</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>5</v>
       </c>
@@ -666,27 +679,27 @@
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <f>A11/A$2</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="D11" s="2">
-        <f>B11/A$2</f>
+        <f t="shared" si="1"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="E11" s="2">
-        <f>C11*(IF(ISERROR(LOG10(C11)),0,LOG10(C11))/C$2)</f>
+        <f>C11*(IF(ISERROR(LOG10(C11)),0,LOG10(C11))/B$2)</f>
         <v>-0.34673344797874411</v>
       </c>
       <c r="F11" s="2">
-        <f>D11*(LOG10(D11)/C$2)</f>
+        <f>D11*(LOG10(D11)/B$2)</f>
         <v>-0.51638712058788683</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.863120568566631</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>6</v>
       </c>
@@ -694,27 +707,27 @@
         <v>1</v>
       </c>
       <c r="C12" s="2">
-        <f>A12/A$2</f>
+        <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="D12" s="2">
-        <f>B12/A$2</f>
+        <f t="shared" si="1"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="E12" s="2">
-        <f>C12*(IF(ISERROR(LOG10(C12)),0,LOG10(C12))/C$2)</f>
+        <f>C12*(IF(ISERROR(LOG10(C12)),0,LOG10(C12))/B$2)</f>
         <v>-0.19062207543124113</v>
       </c>
       <c r="F12" s="2">
-        <f>D12*(LOG10(D12)/C$2)</f>
+        <f>D12*(LOG10(D12)/B$2)</f>
         <v>-0.40105070315108626</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.59167277858232736</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>7</v>
       </c>
@@ -722,23 +735,23 @@
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <f>A13/A$2</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13" s="2">
-        <f>B13/A$2</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E13" s="2">
-        <f>C13*(IF(ISERROR(LOG10(C13)),0,LOG10(C13))/C$2)</f>
+        <f>C13*(IF(ISERROR(LOG10(C13)),0,LOG10(C13))/B$2)</f>
         <v>0</v>
       </c>
       <c r="F13" s="2">
-        <f>D13*(IF(ISERROR(LOG10(D13)),0,LOG10(D13))/C$2)</f>
+        <f>D13*(IF(ISERROR(LOG10(D13)),0,LOG10(D13))/B$2)</f>
         <v>0</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
